--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N83_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N83_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.99471521356157</v>
+        <v>7.961641222203755</v>
       </c>
       <c r="D2" t="n">
-        <v>48.99862233920685</v>
+        <v>7.962276130121114</v>
       </c>
       <c r="E2" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F2" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.97225742557006</v>
+        <v>8.120491831655135</v>
       </c>
       <c r="D3" t="n">
-        <v>49.93858336947955</v>
+        <v>8.115019797540427</v>
       </c>
       <c r="E3" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F3" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.19981047852713</v>
+        <v>8.644969202760659</v>
       </c>
       <c r="D4" t="n">
-        <v>53.15194280888188</v>
+        <v>8.637190706443306</v>
       </c>
       <c r="E4" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F4" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.57062007632339</v>
+        <v>7.080225762402551</v>
       </c>
       <c r="D5" t="n">
-        <v>43.62980106608255</v>
+        <v>7.089842673238414</v>
       </c>
       <c r="E5" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F5" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.33564189163356</v>
+        <v>6.554541807390454</v>
       </c>
       <c r="D6" t="n">
-        <v>40.28697114004621</v>
+        <v>6.546632810257509</v>
       </c>
       <c r="E6" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F6" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.70850446348913</v>
+        <v>5.640131975316985</v>
       </c>
       <c r="D7" t="n">
-        <v>34.77648313021781</v>
+        <v>5.651178508660395</v>
       </c>
       <c r="E7" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F7" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.01699643204451</v>
+        <v>4.390261920207233</v>
       </c>
       <c r="D8" t="n">
-        <v>26.96744560840939</v>
+        <v>4.382209911366526</v>
       </c>
       <c r="E8" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F8" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.46801938871007</v>
+        <v>3.001053150665387</v>
       </c>
       <c r="D9" t="n">
-        <v>18.42149450209222</v>
+        <v>2.993492856589986</v>
       </c>
       <c r="E9" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F9" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>21.09666708728862</v>
+        <v>3.428208401684401</v>
       </c>
       <c r="D10" t="n">
-        <v>21.16015345482022</v>
+        <v>3.438524936408286</v>
       </c>
       <c r="E10" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F10" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>1.528427506781511</v>
+        <v>0.2483694698519956</v>
       </c>
       <c r="D11" t="n">
-        <v>1.575344429233312</v>
+        <v>0.2559934697504132</v>
       </c>
       <c r="E11" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F11" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>8.37872610883597</v>
+        <v>1.361542992685845</v>
       </c>
       <c r="D12" t="n">
-        <v>8.33691920683397</v>
+        <v>1.35474937111052</v>
       </c>
       <c r="E12" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F12" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.454018451475401</v>
+        <v>1.536277998364753</v>
       </c>
       <c r="D13" t="n">
-        <v>9.404400047853608</v>
+        <v>1.528215007776211</v>
       </c>
       <c r="E13" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F13" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.37463726550197</v>
+        <v>4.935878555644071</v>
       </c>
       <c r="D14" t="n">
-        <v>32.96337091661673</v>
+        <v>5.356547773950219</v>
       </c>
       <c r="E14" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F14" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>47.00203717748547</v>
+        <v>7.637831041341389</v>
       </c>
       <c r="D15" t="n">
-        <v>47.08366414425554</v>
+        <v>7.651095423441525</v>
       </c>
       <c r="E15" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F15" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.85827765945713</v>
+        <v>2.739470119661784</v>
       </c>
       <c r="D16" t="n">
-        <v>16.81658482088502</v>
+        <v>2.732695033393816</v>
       </c>
       <c r="E16" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F16" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>8.200609733428363</v>
+        <v>1.332599081682109</v>
       </c>
       <c r="D17" t="n">
-        <v>17.91758117981247</v>
+        <v>2.911606941719526</v>
       </c>
       <c r="E17" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F17" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35.35533905932738</v>
+        <v>5.745242597140699</v>
       </c>
       <c r="D18" t="n">
-        <v>32.23543157254922</v>
+        <v>5.238257630539249</v>
       </c>
       <c r="E18" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F18" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>32.28162685150335</v>
+        <v>5.245764363369294</v>
       </c>
       <c r="D19" t="n">
-        <v>31.92093011644626</v>
+        <v>5.187151143922518</v>
       </c>
       <c r="E19" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F19" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>22.85419768000565</v>
+        <v>3.713807123000918</v>
       </c>
       <c r="D20" t="n">
-        <v>19.7260111209386</v>
+        <v>3.205476807152523</v>
       </c>
       <c r="E20" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F20" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>16.05436496119038</v>
+        <v>2.608834306193437</v>
       </c>
       <c r="D21" t="n">
-        <v>15.82256718600641</v>
+        <v>2.571167167726041</v>
       </c>
       <c r="E21" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F21" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>13.87051127117162</v>
+        <v>2.253958081565388</v>
       </c>
       <c r="D22" t="n">
-        <v>13.09716769158041</v>
+        <v>2.128289749881816</v>
       </c>
       <c r="E22" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F22" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>24.71689144408611</v>
+        <v>4.016494859663992</v>
       </c>
       <c r="D23" t="n">
-        <v>25.71443497978275</v>
+        <v>4.178595684214697</v>
       </c>
       <c r="E23" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F23" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>43.33631507001919</v>
+        <v>7.042151198878119</v>
       </c>
       <c r="D24" t="n">
-        <v>35.59758644692978</v>
+        <v>5.78460779762609</v>
       </c>
       <c r="E24" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F24" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>29.16710424729281</v>
+        <v>4.739654440185081</v>
       </c>
       <c r="D25" t="n">
-        <v>20.25775572209227</v>
+        <v>3.291885304839993</v>
       </c>
       <c r="E25" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F25" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>30.36469644682461</v>
+        <v>4.934263172609</v>
       </c>
       <c r="D26" t="n">
-        <v>29.34053123774846</v>
+        <v>4.767836326134125</v>
       </c>
       <c r="E26" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F26" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>41.85586305273028</v>
+        <v>6.801577746068671</v>
       </c>
       <c r="D27" t="n">
-        <v>40.84465637754293</v>
+        <v>6.637256661350726</v>
       </c>
       <c r="E27" t="n">
-        <v>14.30362067551687</v>
+        <v>2.324338359771491</v>
       </c>
       <c r="F27" t="n">
-        <v>13.78580274621012</v>
+        <v>2.240192946259144</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
